--- a/xls/square_20_tri3_14.xlsx
+++ b/xls/square_20_tri3_14.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>225</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>441</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>864</v>
+      </c>
+      <c r="I12">
+        <v>4.413261420680243</v>
+      </c>
+      <c r="J12">
+        <v>0.7128417276456451</v>
+      </c>
+      <c r="K12">
+        <v>1.4985930268555383</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>441</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1014</v>
+      </c>
+      <c r="I13">
+        <v>3.2525009632355903</v>
+      </c>
+      <c r="J13">
+        <v>-0.09974527984249987</v>
+      </c>
+      <c r="K13">
+        <v>0.8859741361876227</v>
+      </c>
+    </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>
